--- a/Result/profitability/2049.xlsx
+++ b/Result/profitability/2049.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>1.16</v>
       </c>
       <c r="M2" t="n">
-        <v>1.24</v>
+        <v>1.305</v>
       </c>
       <c r="N2" t="n">
-        <v>30.125</v>
+        <v>30.555</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.24</v>
       </c>
       <c r="M3" t="n">
-        <v>1.16</v>
+        <v>1.34375</v>
       </c>
       <c r="N3" t="n">
-        <v>31.55375</v>
+        <v>32.42125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.36</v>
       </c>
       <c r="M4" t="n">
-        <v>1.21375</v>
+        <v>1.34375</v>
       </c>
       <c r="N4" t="n">
-        <v>32.8675</v>
+        <v>33.40875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.23</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0725</v>
+        <v>1.325</v>
       </c>
       <c r="N5" t="n">
-        <v>34.2825</v>
+        <v>34.83625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>-0.08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.015</v>
+        <v>1.1575</v>
       </c>
       <c r="N6" t="n">
-        <v>34.47625</v>
+        <v>35.1725</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8774999999999999</v>
+        <v>1.01375</v>
       </c>
       <c r="N7" t="n">
-        <v>34.59875</v>
+        <v>35.48875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7699999999999999</v>
+        <v>0.865</v>
       </c>
       <c r="N8" t="n">
-        <v>35.50624999999999</v>
+        <v>35.785</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.79</v>
       </c>
       <c r="M9" t="n">
-        <v>0.66375</v>
+        <v>0.6637500000000001</v>
       </c>
       <c r="N9" t="n">
         <v>35.3625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7508</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4943</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2565</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1034</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>13.77%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>46</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1080</v>
+      </c>
+      <c r="K75" t="n">
+        <v>848</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.395</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.9125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4634146341463414</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06981840951784601</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>5.315789473684211</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.430000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.148957632817754</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
